--- a/03_Private_Equity/deals/PROJECT_ATLAS.xlsx
+++ b/03_Private_Equity/deals/PROJECT_ATLAS.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="121">
   <si>
     <t xml:space="preserve">[TARGET] — LBO Model</t>
   </si>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Check (sources = uses):</t>
   </si>
   <si>
-    <t xml:space="preserve">Debt Schedule (with cash sweep)</t>
+    <t xml:space="preserve">Debt Schedule — Revolver / TLA / TLB (with cash sweep)</t>
   </si>
   <si>
     <t xml:space="preserve">Yr0</t>
@@ -150,48 +150,93 @@
     <t xml:space="preserve">Entry EBITDA growth (%/yr)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cash flow available for debt paydown (FCF)</t>
+    <t xml:space="preserve">Cash flow available for debt service (FCF)</t>
   </si>
   <si>
     <t xml:space="preserve">FCF conversion (FCF / EBITDA, %)</t>
   </si>
   <si>
-    <t xml:space="preserve">Mandatory amort (% of original TLB/yr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cash sweep (% of excess FCF, after debt svc)</t>
+    <t xml:space="preserve">TLA mandatory amort (% of original/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revolving Credit Facility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLA interest rate (%)</t>
   </si>
   <si>
     <t xml:space="preserve">  Beginning balance</t>
   </si>
   <si>
-    <t xml:space="preserve">Term Loan B interest rate (%)</t>
+    <t xml:space="preserve">TLB mandatory amort (% of original/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Interest expense (rate x beginning balance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLB interest rate (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Cash available for revolver / sweep decisions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash sweep (% of excess cash, after revolver)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Draw / (repayment)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revolver commitment / capacity ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Ending balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revolver interest rate (%, on drawn balance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Excess cash remaining for term loan sweep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original TLA balance (Yr0, $)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original TLB balance (Yr0, $)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Term Loan A (senior, amortizing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revolver drawn at close ($)</t>
   </si>
   <si>
     <t xml:space="preserve">  Mandatory amortization</t>
   </si>
   <si>
-    <t xml:space="preserve">Original TLB balance (Yr0, $)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Cash sweep (excess FCF after debt svc)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Ending balance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Models Term Loan B only — the amortizing/sweep tranche in a typical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Interest expense (rate x beginning balance)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">structure. Revolver stays undrawn at close; notes are bullet/no-amort.</t>
+    <t xml:space="preserve">Revolver commitment (K12) is total facility SIZE available to draw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Cash sweep (after revolver fully repaid)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">against, separate from Sources &amp; Uses' 'drawn at close' amount (K16),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">which is typically 0 for a fresh LBO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Term Loan B (junior)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Cash sweep (only after TLA fully repaid)</t>
   </si>
   <si>
     <t xml:space="preserve">Total debt (end of period)</t>
   </si>
   <si>
+    <t xml:space="preserve">Total interest expense</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total debt / EBITDA (leverage)</t>
   </si>
   <si>
@@ -231,10 +276,13 @@
     <t xml:space="preserve">Exit equity value</t>
   </si>
   <si>
-    <t xml:space="preserve">Returns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOIC</t>
+    <t xml:space="preserve">Deal-Level Returns (blended, before management promote)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOIC (exit equity value / ALL invested equity, sponsor + mgmt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everyone's return before the promote reallocates value from sponsor to management below — not the sponsor's actual net return</t>
   </si>
   <si>
     <t xml:space="preserve">Hold period (yrs)</t>
@@ -243,6 +291,45 @@
     <t xml:space="preserve">IRR</t>
   </si>
   <si>
+    <t xml:space="preserve">Management Promote / Ratchet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total sponsor + management invested equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Management rollover % of total equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRR hurdle for promote to kick in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Management promote % of value created above hurdle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hurdle equity value (invested equity grown at hurdle IRR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value created above hurdle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Management promote ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Management total proceeds (pro-rata rollover + promote)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sponsor net proceeds (exit equity value less management take)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sponsor-only MOIC (on sponsor equity, net of promote paid away)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sponsor-only IRR (net of promote paid away)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is the number that actually matters to the sponsor's LPs — the blended IRR above overstates what the fund itself earns once management's promote is paid away</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sensitivity — IRR by Entry/Exit Multiple</t>
   </si>
   <si>
@@ -273,7 +360,7 @@
     <t xml:space="preserve">Deal close</t>
   </si>
   <si>
-    <t xml:space="preserve">Instance created at financial close; Sources &amp; Uses and debt terms locked from illustrative deal docs.</t>
+    <t xml:space="preserve">Instance created at financial close; two-tranche debt structure (TLA senior/amortizing + TLB junior) locked from illustrative deal docs, plus a $40mm revolver backstop.</t>
   </si>
   <si>
     <t xml:space="preserve">Reviewed sources=uses check ties to 0</t>
@@ -288,7 +375,7 @@
     <t xml:space="preserve">Quarterly review</t>
   </si>
   <si>
-    <t xml:space="preserve">No covenant changes; rolled forward leverage check against latest illustrative EBITDA run-rate.</t>
+    <t xml:space="preserve">No covenant changes; confirmed cash sweep correctly prioritizing TLA paydown before TLB per credit agreement waterfall.</t>
   </si>
   <si>
     <t xml:space="preserve">Leverage trending down as modeled</t>
@@ -297,10 +384,10 @@
     <t xml:space="preserve">Manual review</t>
   </si>
   <si>
-    <t xml:space="preserve">Refreshed Cover date; caught and fixed a Cover-tab field-order bug in the underlying LBO template (Last refreshed/next-date cells were misaligned with the weekly refresh checker) as part of this refresh.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recalc clean, debt paydown schedule tracking model</t>
+    <t xml:space="preserve">Rebuilt against the new multi-tranche debt schedule (revolver/TLA/TLB) and added the management promote/ratchet analysis; refreshed Cover date.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recalc clean; sponsor-net IRR now shown separately from blended IRR</t>
   </si>
 </sst>
 </file>
@@ -464,7 +551,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -529,11 +616,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -562,6 +653,22 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -942,7 +1049,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>600</v>
+        <v>750</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -950,7 +1057,7 @@
         <v>19</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>20</v>
@@ -964,13 +1071,13 @@
         <v>21</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -984,7 +1091,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -998,7 +1105,7 @@
         <v>26</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1013,7 +1120,7 @@
       </c>
       <c r="F10" s="8" t="n">
         <f aca="false">SUM(F5:F9)</f>
-        <v>700</v>
+        <v>850</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1022,7 +1129,7 @@
       </c>
       <c r="C11" s="8" t="n">
         <f aca="false">SUM(C5:C10)</f>
-        <v>700</v>
+        <v>850</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1050,14 +1157,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:K16"/>
+  <dimension ref="B2:K32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14"/>
   </cols>
   <sheetData>
@@ -1165,240 +1272,641 @@
         <v>43</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>0.75</v>
+        <v>45</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>0.065</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <f aca="false">$K$10</f>
-        <v>350</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <f aca="false">C12</f>
-        <v>331.5</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <f aca="false">D12</f>
-        <v>309.27625</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <f aca="false">E12</f>
-        <v>282.928896875</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <f aca="false">F12</f>
-        <v>252.022187414063</v>
-      </c>
-      <c r="H9" s="16" t="n">
-        <f aca="false">G12</f>
-        <v>216.081510464512</v>
+        <v>46</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <f aca="false">$K$16</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <f aca="false">C13</f>
+        <v>0.499999999999993</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <f aca="false">D13</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <f aca="false">E13</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <f aca="false">F13</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <f aca="false">G13</f>
+        <v>0</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="K9" s="17" t="n">
-        <v>0.09</v>
+        <v>47</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="16" t="n">
-        <f aca="false">MIN($K$10*$K$7,C9)</f>
-        <v>3.5</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <f aca="false">MIN($K$10*$K$7,D9)</f>
-        <v>3.5</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <f aca="false">MIN($K$10*$K$7,E9)</f>
-        <v>3.5</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <f aca="false">MIN($K$10*$K$7,F9)</f>
-        <v>3.5</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <f aca="false">MIN($K$10*$K$7,G9)</f>
-        <v>3.5</v>
-      </c>
-      <c r="H10" s="16" t="n">
-        <f aca="false">MIN($K$10*$K$7,H9)</f>
-        <v>3.5</v>
-      </c>
-      <c r="J10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="K10" s="13" t="n">
-        <f aca="false">'Sources &amp; Uses'!C7</f>
-        <v>350</v>
+      <c r="C10" s="17" t="n">
+        <f aca="false">C9*$K$13</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <f aca="false">D9*$K$13</f>
+        <v>0.0374999999999995</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <f aca="false">E9*$K$13</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <f aca="false">F9*$K$13</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <f aca="false">G9*$K$13</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <f aca="false">H9*$K$13</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" s="16" t="n">
+        <v>0.095</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <f aca="false">MIN(MAX(0,$K$8*(C6-C10-C13)),C9-C10)</f>
-        <v>15</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <f aca="false">MIN(MAX(0,$K$8*(D6-D10-D13)),D9-D10)</f>
-        <v>18.72375</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <f aca="false">MIN(MAX(0,$K$8*(E6-E10-E13)),E9-E10)</f>
-        <v>22.847353125</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <f aca="false">MIN(MAX(0,$K$8*(F6-F10-F13)),F9-F10)</f>
-        <v>27.4067094609375</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <f aca="false">MIN(MAX(0,$K$8*(G6-G10-G13)),G9-G10)</f>
-        <v>32.4406769495508</v>
-      </c>
-      <c r="H11" s="16" t="n">
-        <f aca="false">MIN(MAX(0,$K$8*(H6-H10-H13)),H9-H10)</f>
-        <v>37.9913031196455</v>
+        <v>50</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <f aca="false">C6-C18-C25-C10-C21-C28</f>
+        <v>-0.499999999999993</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <f aca="false">D6-D18-D25-D10-D21-D28</f>
+        <v>3.9275</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <f aca="false">E6-E18-E25-E10-E21-E28</f>
+        <v>8.795090625</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <f aca="false">F6-F18-F25-F10-F21-F28</f>
+        <v>14.0967312929688</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <f aca="false">G6-G18-G25-G10-G21-G28</f>
+        <v>19.879299743501</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <f aca="false">H6-H18-H25-H10-H21-H28</f>
+        <v>26.1795895739967</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="16" t="n">
-        <f aca="false">C9-C10-C11</f>
-        <v>331.5</v>
-      </c>
-      <c r="D12" s="16" t="n">
-        <f aca="false">D9-D10-D11</f>
-        <v>309.27625</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <f aca="false">E9-E10-E11</f>
-        <v>282.928896875</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <f aca="false">F9-F10-F11</f>
-        <v>252.022187414063</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <f aca="false">G9-G10-G11</f>
-        <v>216.081510464512</v>
-      </c>
-      <c r="H12" s="16" t="n">
-        <f aca="false">H9-H10-H11</f>
-        <v>174.590207344866</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <f aca="false">IF(C11&lt;0,MIN(-C11,$K$12-C9),-MIN(C9,MAX(0,C11)))</f>
+        <v>0.499999999999993</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <f aca="false">IF(D11&lt;0,MIN(-D11,$K$12-D9),-MIN(D9,MAX(0,D11)))</f>
+        <v>-0.499999999999993</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <f aca="false">IF(E11&lt;0,MIN(-E11,$K$12-E9),-MIN(E9,MAX(0,E11)))</f>
+        <v>-0</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <f aca="false">IF(F11&lt;0,MIN(-F11,$K$12-F9),-MIN(F9,MAX(0,F11)))</f>
+        <v>-0</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <f aca="false">IF(G11&lt;0,MIN(-G11,$K$12-G9),-MIN(G9,MAX(0,G11)))</f>
+        <v>-0</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <f aca="false">IF(H11&lt;0,MIN(-H11,$K$12-H9),-MIN(H9,MAX(0,H11)))</f>
+        <v>-0</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <f aca="false">C9*$K$9</f>
-        <v>31.5</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <f aca="false">D9*$K$9</f>
-        <v>29.835</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <f aca="false">E9*$K$9</f>
-        <v>27.8348625</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <f aca="false">F9*$K$9</f>
-        <v>25.46360071875</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <f aca="false">G9*$K$9</f>
-        <v>22.6819968672656</v>
-      </c>
-      <c r="H13" s="16" t="n">
-        <f aca="false">H9*$K$9</f>
-        <v>19.4473359418061</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <f aca="false">C9+C12</f>
+        <v>0.499999999999993</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <f aca="false">D9+D12</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <f aca="false">E9+E12</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <f aca="false">F9+F12</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <f aca="false">G9+G12</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <f aca="false">H9+H12</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K13" s="16" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <f aca="false">MAX(0,MAX(0,C11)-C9)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <f aca="false">MAX(0,MAX(0,D11)-D9)</f>
+        <v>3.42750000000001</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <f aca="false">MAX(0,MAX(0,E11)-E9)</f>
+        <v>8.795090625</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <f aca="false">MAX(0,MAX(0,F11)-F9)</f>
+        <v>14.0967312929688</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <f aca="false">MAX(0,MAX(0,G11)-G9)</f>
+        <v>19.879299743501</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <f aca="false">MAX(0,MAX(0,H11)-H9)</f>
+        <v>26.1795895739967</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K14" s="13" t="n">
+        <f aca="false">'Sources &amp; Uses'!C6</f>
+        <v>300</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <f aca="false">C12</f>
-        <v>331.5</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <f aca="false">D12</f>
-        <v>309.27625</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <f aca="false">E12</f>
-        <v>282.928896875</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <f aca="false">F12</f>
-        <v>252.022187414063</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <f aca="false">G12</f>
-        <v>216.081510464512</v>
-      </c>
-      <c r="H15" s="9" t="n">
-        <f aca="false">H12</f>
-        <v>174.590207344866</v>
+      <c r="J15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="K15" s="13" t="n">
+        <f aca="false">'Sources &amp; Uses'!C7</f>
+        <v>200</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="19" t="n">
-        <f aca="false">IFERROR(C15/C5,"-")</f>
-        <v>3.315</v>
-      </c>
-      <c r="D16" s="19" t="n">
-        <f aca="false">IFERROR(D15/D5,"-")</f>
-        <v>2.91770047169811</v>
-      </c>
-      <c r="E16" s="19" t="n">
-        <f aca="false">IFERROR(E15/E5,"-")</f>
-        <v>2.51805710995906</v>
-      </c>
-      <c r="F16" s="19" t="n">
-        <f aca="false">IFERROR(F15/F5,"-")</f>
-        <v>2.11602688304828</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <f aca="false">IFERROR(G15/G5,"-")</f>
-        <v>1.7115679518184</v>
-      </c>
-      <c r="H16" s="19" t="n">
-        <f aca="false">IFERROR(H15/H5,"-")</f>
-        <v>1.30463959340831</v>
+        <v>59</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K16" s="13" t="n">
+        <f aca="false">'Sources &amp; Uses'!C5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <f aca="false">$K$14</f>
+        <v>300</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <f aca="false">C20</f>
+        <v>285</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <f aca="false">D20</f>
+        <v>267.429375</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <f aca="false">E20</f>
+        <v>245.83305703125</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <f aca="false">F20</f>
+        <v>220.260508561523</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <f aca="false">G20</f>
+        <v>190.351033753898</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <f aca="false">MIN($K$14*$K$7,C17)</f>
+        <v>15</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <f aca="false">MIN($K$14*$K$7,D17)</f>
+        <v>15</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <f aca="false">MIN($K$14*$K$7,E17)</f>
+        <v>15</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <f aca="false">MIN($K$14*$K$7,F17)</f>
+        <v>15</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <f aca="false">MIN($K$14*$K$7,G17)</f>
+        <v>15</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <f aca="false">MIN($K$14*$K$7,H17)</f>
+        <v>15</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <f aca="false">MIN($K$11*C14,C17-C18)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <f aca="false">MIN($K$11*D14,D17-D18)</f>
+        <v>2.57062500000001</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <f aca="false">MIN($K$11*E14,E17-E18)</f>
+        <v>6.59631796875</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <f aca="false">MIN($K$11*F14,F17-F18)</f>
+        <v>10.5725484697266</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <f aca="false">MIN($K$11*G14,G17-G18)</f>
+        <v>14.9094748076257</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <f aca="false">MIN($K$11*H14,H17-H18)</f>
+        <v>19.6346921804975</v>
+      </c>
+      <c r="J19" s="19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <f aca="false">C17-C18-C19</f>
+        <v>285</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <f aca="false">D17-D18-D19</f>
+        <v>267.429375</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <f aca="false">E17-E18-E19</f>
+        <v>245.83305703125</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <f aca="false">F17-F18-F19</f>
+        <v>220.260508561523</v>
+      </c>
+      <c r="G20" s="17" t="n">
+        <f aca="false">G17-G18-G19</f>
+        <v>190.351033753898</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <f aca="false">H17-H18-H19</f>
+        <v>155.7163415734</v>
+      </c>
+      <c r="J20" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <f aca="false">C17*$K$8</f>
+        <v>19.5</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <f aca="false">D17*$K$8</f>
+        <v>18.525</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <f aca="false">E17*$K$8</f>
+        <v>17.382909375</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <f aca="false">F17*$K$8</f>
+        <v>15.9791487070313</v>
+      </c>
+      <c r="G21" s="17" t="n">
+        <f aca="false">G17*$K$8</f>
+        <v>14.316933056499</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <f aca="false">H17*$K$8</f>
+        <v>12.3728171940034</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <f aca="false">$K$15</f>
+        <v>200</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <f aca="false">C27</f>
+        <v>198</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <f aca="false">D27</f>
+        <v>196</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <f aca="false">E27</f>
+        <v>194</v>
+      </c>
+      <c r="G24" s="17" t="n">
+        <f aca="false">F27</f>
+        <v>192</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <f aca="false">G27</f>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <f aca="false">MIN($K$15*$K$9,C24)</f>
+        <v>2</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <f aca="false">MIN($K$15*$K$9,D24)</f>
+        <v>2</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <f aca="false">MIN($K$15*$K$9,E24)</f>
+        <v>2</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <f aca="false">MIN($K$15*$K$9,F24)</f>
+        <v>2</v>
+      </c>
+      <c r="G25" s="17" t="n">
+        <f aca="false">MIN($K$15*$K$9,G24)</f>
+        <v>2</v>
+      </c>
+      <c r="H25" s="17" t="n">
+        <f aca="false">MIN($K$15*$K$9,H24)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <f aca="false">MIN($K$11*C14-C19,C24-C25)</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <f aca="false">MIN($K$11*D14-D19,D24-D25)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <f aca="false">MIN($K$11*E14-E19,E24-E25)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <f aca="false">MIN($K$11*F14-F19,F24-F25)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="17" t="n">
+        <f aca="false">MIN($K$11*G14-G19,G24-G25)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <f aca="false">MIN($K$11*H14-H19,H24-H25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="17" t="n">
+        <f aca="false">C24-C25-C26</f>
+        <v>198</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <f aca="false">D24-D25-D26</f>
+        <v>196</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <f aca="false">E24-E25-E26</f>
+        <v>194</v>
+      </c>
+      <c r="F27" s="17" t="n">
+        <f aca="false">F24-F25-F26</f>
+        <v>192</v>
+      </c>
+      <c r="G27" s="17" t="n">
+        <f aca="false">G24-G25-G26</f>
+        <v>190</v>
+      </c>
+      <c r="H27" s="17" t="n">
+        <f aca="false">H24-H25-H26</f>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="17" t="n">
+        <f aca="false">C24*$K$10</f>
+        <v>19</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <f aca="false">D24*$K$10</f>
+        <v>18.81</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <f aca="false">E24*$K$10</f>
+        <v>18.62</v>
+      </c>
+      <c r="F28" s="17" t="n">
+        <f aca="false">F24*$K$10</f>
+        <v>18.43</v>
+      </c>
+      <c r="G28" s="17" t="n">
+        <f aca="false">G24*$K$10</f>
+        <v>18.24</v>
+      </c>
+      <c r="H28" s="17" t="n">
+        <f aca="false">H24*$K$10</f>
+        <v>18.05</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="9" t="n">
+        <f aca="false">C13+C20+C27</f>
+        <v>483.5</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <f aca="false">D13+D20+D27</f>
+        <v>463.429375</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <f aca="false">E13+E20+E27</f>
+        <v>439.83305703125</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <f aca="false">F13+F20+F27</f>
+        <v>412.260508561523</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <f aca="false">G13+G20+G27</f>
+        <v>380.351033753898</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <f aca="false">H13+H20+H27</f>
+        <v>343.7163415734</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <f aca="false">C10+C21+C28</f>
+        <v>38.5</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <f aca="false">D10+D21+D28</f>
+        <v>37.3725</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <f aca="false">E10+E21+E28</f>
+        <v>36.002909375</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <f aca="false">F10+F21+F28</f>
+        <v>34.4091487070313</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <f aca="false">G10+G21+G28</f>
+        <v>32.556933056499</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <f aca="false">H10+H21+H28</f>
+        <v>30.4228171940034</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="20" t="n">
+        <f aca="false">IFERROR(C30/C5,"-")</f>
+        <v>4.835</v>
+      </c>
+      <c r="D32" s="20" t="n">
+        <f aca="false">IFERROR(D30/D5,"-")</f>
+        <v>4.37197523584906</v>
+      </c>
+      <c r="E32" s="20" t="n">
+        <f aca="false">IFERROR(E30/E5,"-")</f>
+        <v>3.91449854958393</v>
+      </c>
+      <c r="F32" s="20" t="n">
+        <f aca="false">IFERROR(F30/F5,"-")</f>
+        <v>3.46141872620958</v>
+      </c>
+      <c r="G32" s="20" t="n">
+        <f aca="false">IFERROR(G30/G5,"-")</f>
+        <v>3.01273643642493</v>
+      </c>
+      <c r="H32" s="20" t="n">
+        <f aca="false">IFERROR(H30/H5,"-")</f>
+        <v>2.56844845388345</v>
       </c>
     </row>
   </sheetData>
@@ -1417,7 +1925,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C20"/>
+  <dimension ref="B2:D33"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
@@ -1427,114 +1935,117 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="5" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="20" t="n">
+        <v>73</v>
+      </c>
+      <c r="C5" s="21" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="21" t="n">
-        <v>7</v>
+        <v>74</v>
+      </c>
+      <c r="C6" s="22" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C7" s="9" t="n">
         <f aca="false">C5*C6</f>
-        <v>700</v>
+        <v>750</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="22" t="n">
+        <v>76</v>
+      </c>
+      <c r="C8" s="23" t="n">
         <f aca="false">'Sources &amp; Uses'!C9</f>
         <v>200</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="22" t="n">
+        <v>78</v>
+      </c>
+      <c r="C11" s="23" t="n">
         <f aca="false">'Debt Schedule'!H5</f>
         <v>133.82255776</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="21" t="n">
-        <v>7.5</v>
+        <v>79</v>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C13" s="9" t="n">
         <f aca="false">C11*C12</f>
-        <v>1003.6691832</v>
+        <v>1070.58046208</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="22" t="n">
-        <f aca="false">'Debt Schedule'!H15</f>
-        <v>174.590207344866</v>
+        <v>81</v>
+      </c>
+      <c r="C14" s="23" t="n">
+        <f aca="false">'Debt Schedule'!H30</f>
+        <v>343.7163415734</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="C15" s="8" t="n">
         <f aca="false">C13-C14</f>
-        <v>829.078975855134</v>
+        <v>726.8641205066</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="23" t="n">
-        <f aca="false">IFERROR(C15/C8,"-")</f>
-        <v>4.14539487927567</v>
+        <v>84</v>
+      </c>
+      <c r="C18" s="24" t="n">
+        <f aca="false">IFERROR(C15/(C8+'Sources &amp; Uses'!C10),"-")</f>
+        <v>2.9074564820264</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="C19" s="12" t="n">
         <f aca="false">Cover!C9</f>
@@ -1543,11 +2054,116 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="24" t="n">
+        <v>87</v>
+      </c>
+      <c r="C20" s="25" t="n">
         <f aca="false">IFERROR(C18^(1/C19)-1,"-")</f>
-        <v>0.328963892040467</v>
+        <v>0.237948690048196</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <f aca="false">'Sources &amp; Uses'!C9+'Sources &amp; Uses'!C10</f>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="26" t="n">
+        <f aca="false">IFERROR('Sources &amp; Uses'!C10/C23,"-")</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" s="14" t="n">
+        <f aca="false">IFERROR(C23*(1+C25)^C19,"-")</f>
+        <v>622.08</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="14" t="n">
+        <f aca="false">MAX(0,C15-C27)</f>
+        <v>104.7841205066</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="27" t="n">
+        <f aca="false">C28*C26</f>
+        <v>20.95682410132</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="27" t="n">
+        <f aca="false">IFERROR(C24*C15+C29,"-")</f>
+        <v>166.32964820264</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" s="27" t="n">
+        <f aca="false">IFERROR(C15-C30,"-")</f>
+        <v>560.53447230396</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" s="28" t="n">
+        <f aca="false">IFERROR(C31/'Sources &amp; Uses'!C9,"-")</f>
+        <v>2.8026723615198</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" s="29" t="n">
+        <f aca="false">IFERROR(C32^(1/C19)-1,"-")</f>
+        <v>0.228894119802123</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1576,127 +2192,127 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="25" t="n">
+        <v>102</v>
+      </c>
+      <c r="C4" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="D4" s="25" t="n">
+      <c r="D4" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="F4" s="25" t="n">
+      <c r="F4" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="25" t="n">
+      <c r="G4" s="30" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>74</v>
+      <c r="C5" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>74</v>
+      <c r="C6" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>74</v>
+      <c r="C7" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>74</v>
+      <c r="C8" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>74</v>
+      <c r="C9" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1727,24 +2343,24 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="10" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1752,30 +2368,30 @@
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>6</v>
@@ -1786,13 +2402,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>8</v>

--- a/03_Private_Equity/deals/PROJECT_ATLAS.xlsx
+++ b/03_Private_Equity/deals/PROJECT_ATLAS.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="126">
   <si>
     <t xml:space="preserve">[TARGET] — LBO Model</t>
   </si>
@@ -69,6 +69,12 @@
     <t xml:space="preserve">Weekly</t>
   </si>
   <si>
+    <t xml:space="preserve">Active scenario (Base or Downside):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sources &amp; Uses</t>
   </si>
   <si>
@@ -144,6 +150,12 @@
     <t xml:space="preserve">Assumptions</t>
   </si>
   <si>
+    <t xml:space="preserve">Downside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active</t>
+  </si>
+  <si>
     <t xml:space="preserve">EBITDA</t>
   </si>
   <si>
@@ -213,16 +225,19 @@
     <t xml:space="preserve">  Mandatory amortization</t>
   </si>
   <si>
-    <t xml:space="preserve">Revolver commitment (K12) is total facility SIZE available to draw</t>
+    <t xml:space="preserve">Deal terms (rows 14-16) don't vary by scenario, so they skip the</t>
   </si>
   <si>
     <t xml:space="preserve">  Cash sweep (after revolver fully repaid)</t>
   </si>
   <si>
-    <t xml:space="preserve">against, separate from Sources &amp; Uses' 'drawn at close' amount (K16),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">which is typically 0 for a fresh LBO.</t>
+    <t xml:space="preserve">Base/Downside split and go straight in the Active column. Revolver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commitment (M12) is total facility SIZE available to draw against,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">separate from the 'drawn at close' amount (M16, typically 0).</t>
   </si>
   <si>
     <t xml:space="preserve">Term Loan B (junior)</t>
@@ -264,7 +279,7 @@
     <t xml:space="preserve">Exit EBITDA (Yr5)</t>
   </si>
   <si>
-    <t xml:space="preserve">Exit multiple</t>
+    <t xml:space="preserve">Exit multiple (Active)</t>
   </si>
   <si>
     <t xml:space="preserve">Exit EV</t>
@@ -384,10 +399,10 @@
     <t xml:space="preserve">Manual review</t>
   </si>
   <si>
-    <t xml:space="preserve">Rebuilt against the new multi-tranche debt schedule (revolver/TLA/TLB) and added the management promote/ratchet analysis; refreshed Cover date.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recalc clean; sponsor-net IRR now shown separately from blended IRR</t>
+    <t xml:space="preserve">Added Base/Downside scenario switching (Cover C11) and scenario-aware exit multiple; ran both cases to confirm Downside shows materially worse leverage and returns, not just a different point estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base MOIC ~2.9x, Downside case shows meaningful equity value erosion -- flagged for IC discussion</t>
   </si>
 </sst>
 </file>
@@ -551,7 +566,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -596,10 +611,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -616,10 +627,18 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -648,15 +667,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -928,7 +947,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C10"/>
+  <dimension ref="B2:C11"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
@@ -996,6 +1015,14 @@
       </c>
       <c r="C10" s="4" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1027,26 +1054,26 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>750</v>
@@ -1054,13 +1081,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>300</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F6" s="7" t="n">
         <v>50</v>
@@ -1068,13 +1095,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>200</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>20</v>
@@ -1082,13 +1109,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>100</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>15</v>
@@ -1096,13 +1123,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>200</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>15</v>
@@ -1110,13 +1137,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>50</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F10" s="8" t="n">
         <f aca="false">SUM(F5:F9)</f>
@@ -1125,7 +1152,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" s="8" t="n">
         <f aca="false">SUM(C5:C10)</f>
@@ -1134,7 +1161,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C13" s="9" t="n">
         <f aca="false">C11-F10</f>
@@ -1157,674 +1184,749 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:K32"/>
+  <dimension ref="B2:M32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C4" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" s="11"/>
+        <v>40</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="13" t="n">
+      <c r="B5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="12" t="n">
         <f aca="false">Returns!C5</f>
         <v>100</v>
       </c>
-      <c r="D5" s="14" t="n">
-        <f aca="false">C5*(1+$K$5)</f>
+      <c r="D5" s="13" t="n">
+        <f aca="false">C5*(1+$M$5)</f>
         <v>106</v>
       </c>
-      <c r="E5" s="14" t="n">
-        <f aca="false">D5*(1+$K$5)</f>
+      <c r="E5" s="13" t="n">
+        <f aca="false">D5*(1+$M$5)</f>
         <v>112.36</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <f aca="false">E5*(1+$K$5)</f>
+      <c r="F5" s="13" t="n">
+        <f aca="false">E5*(1+$M$5)</f>
         <v>119.1016</v>
       </c>
-      <c r="G5" s="14" t="n">
-        <f aca="false">F5*(1+$K$5)</f>
+      <c r="G5" s="13" t="n">
+        <f aca="false">F5*(1+$M$5)</f>
         <v>126.247696</v>
       </c>
-      <c r="H5" s="14" t="n">
-        <f aca="false">G5*(1+$K$5)</f>
+      <c r="H5" s="13" t="n">
+        <f aca="false">G5*(1+$M$5)</f>
         <v>133.82255776</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" s="15" t="n">
+        <v>44</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M5" s="15" t="n">
+        <f aca="false">IF(Cover!$C$11="Downside",L5,K5)</f>
         <v>0.06</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="14" t="n">
-        <f aca="false">C5*$K$6</f>
+        <v>45</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <f aca="false">C5*$M$6</f>
         <v>55</v>
       </c>
-      <c r="D6" s="14" t="n">
-        <f aca="false">D5*$K$6</f>
+      <c r="D6" s="13" t="n">
+        <f aca="false">D5*$M$6</f>
         <v>58.3</v>
       </c>
-      <c r="E6" s="14" t="n">
-        <f aca="false">E5*$K$6</f>
+      <c r="E6" s="13" t="n">
+        <f aca="false">E5*$M$6</f>
         <v>61.798</v>
       </c>
-      <c r="F6" s="14" t="n">
-        <f aca="false">F5*$K$6</f>
+      <c r="F6" s="13" t="n">
+        <f aca="false">F5*$M$6</f>
         <v>65.50588</v>
       </c>
-      <c r="G6" s="14" t="n">
-        <f aca="false">G5*$K$6</f>
+      <c r="G6" s="13" t="n">
+        <f aca="false">G5*$M$6</f>
         <v>69.4362328</v>
       </c>
-      <c r="H6" s="14" t="n">
-        <f aca="false">H5*$K$6</f>
+      <c r="H6" s="13" t="n">
+        <f aca="false">H5*$M$6</f>
         <v>73.602406768</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K6" s="15" t="n">
+        <v>46</v>
+      </c>
+      <c r="K6" s="14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L6" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M6" s="15" t="n">
+        <f aca="false">IF(Cover!$C$11="Downside",L6,K6)</f>
         <v>0.55</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J7" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K7" s="15" t="n">
+        <v>47</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L7" s="14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M7" s="15" t="n">
+        <f aca="false">IF(Cover!$C$11="Downside",L7,K7)</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K8" s="16" t="n">
         <v>0.065</v>
       </c>
+      <c r="L8" s="16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M8" s="17" t="n">
+        <f aca="false">IF(Cover!$C$11="Downside",L8,K8)</f>
+        <v>0.065</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="17" t="n">
-        <f aca="false">$K$16</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <f aca="false">$M$16</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="18" t="n">
         <f aca="false">C13</f>
         <v>0.499999999999993</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <f aca="false">D13</f>
         <v>0</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="18" t="n">
         <f aca="false">E13</f>
         <v>0</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="18" t="n">
         <f aca="false">F13</f>
         <v>0</v>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="H9" s="18" t="n">
         <f aca="false">G13</f>
         <v>0</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="K9" s="15" t="n">
+        <v>51</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L9" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M9" s="15" t="n">
+        <f aca="false">IF(Cover!$C$11="Downside",L9,K9)</f>
         <v>0.01</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="17" t="n">
-        <f aca="false">C9*$K$13</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="17" t="n">
-        <f aca="false">D9*$K$13</f>
+        <v>52</v>
+      </c>
+      <c r="C10" s="18" t="n">
+        <f aca="false">C9*$M$13</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <f aca="false">D9*$M$13</f>
         <v>0.0374999999999995</v>
       </c>
-      <c r="E10" s="17" t="n">
-        <f aca="false">E9*$K$13</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="17" t="n">
-        <f aca="false">F9*$K$13</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="17" t="n">
-        <f aca="false">G9*$K$13</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="17" t="n">
-        <f aca="false">H9*$K$13</f>
+      <c r="E10" s="18" t="n">
+        <f aca="false">E9*$M$13</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <f aca="false">F9*$M$13</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <f aca="false">G9*$M$13</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <f aca="false">H9*$M$13</f>
         <v>0</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K10" s="16" t="n">
         <v>0.095</v>
       </c>
+      <c r="L10" s="16" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="M10" s="17" t="n">
+        <f aca="false">IF(Cover!$C$11="Downside",L10,K10)</f>
+        <v>0.095</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="C11" s="18" t="n">
         <f aca="false">C6-C18-C25-C10-C21-C28</f>
         <v>-0.499999999999993</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="18" t="n">
         <f aca="false">D6-D18-D25-D10-D21-D28</f>
         <v>3.9275</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <f aca="false">E6-E18-E25-E10-E21-E28</f>
         <v>8.795090625</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="18" t="n">
         <f aca="false">F6-F18-F25-F10-F21-F28</f>
         <v>14.0967312929688</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="18" t="n">
         <f aca="false">G6-G18-G25-G10-G21-G28</f>
         <v>19.879299743501</v>
       </c>
-      <c r="H11" s="17" t="n">
+      <c r="H11" s="18" t="n">
         <f aca="false">H6-H18-H25-H10-H21-H28</f>
         <v>26.1795895739967</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="K11" s="15" t="n">
+        <v>55</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L11" s="14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M11" s="15" t="n">
+        <f aca="false">IF(Cover!$C$11="Downside",L11,K11)</f>
         <v>0.75</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <f aca="false">IF(C11&lt;0,MIN(-C11,$K$12-C9),-MIN(C9,MAX(0,C11)))</f>
+        <v>56</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <f aca="false">IF(C11&lt;0,MIN(-C11,$M$12-C9),-MIN(C9,MAX(0,C11)))</f>
         <v>0.499999999999993</v>
       </c>
-      <c r="D12" s="17" t="n">
-        <f aca="false">IF(D11&lt;0,MIN(-D11,$K$12-D9),-MIN(D9,MAX(0,D11)))</f>
+      <c r="D12" s="18" t="n">
+        <f aca="false">IF(D11&lt;0,MIN(-D11,$M$12-D9),-MIN(D9,MAX(0,D11)))</f>
         <v>-0.499999999999993</v>
       </c>
-      <c r="E12" s="17" t="n">
-        <f aca="false">IF(E11&lt;0,MIN(-E11,$K$12-E9),-MIN(E9,MAX(0,E11)))</f>
+      <c r="E12" s="18" t="n">
+        <f aca="false">IF(E11&lt;0,MIN(-E11,$M$12-E9),-MIN(E9,MAX(0,E11)))</f>
         <v>-0</v>
       </c>
-      <c r="F12" s="17" t="n">
-        <f aca="false">IF(F11&lt;0,MIN(-F11,$K$12-F9),-MIN(F9,MAX(0,F11)))</f>
+      <c r="F12" s="18" t="n">
+        <f aca="false">IF(F11&lt;0,MIN(-F11,$M$12-F9),-MIN(F9,MAX(0,F11)))</f>
         <v>-0</v>
       </c>
-      <c r="G12" s="17" t="n">
-        <f aca="false">IF(G11&lt;0,MIN(-G11,$K$12-G9),-MIN(G9,MAX(0,G11)))</f>
+      <c r="G12" s="18" t="n">
+        <f aca="false">IF(G11&lt;0,MIN(-G11,$M$12-G9),-MIN(G9,MAX(0,G11)))</f>
         <v>-0</v>
       </c>
-      <c r="H12" s="17" t="n">
-        <f aca="false">IF(H11&lt;0,MIN(-H11,$K$12-H9),-MIN(H9,MAX(0,H11)))</f>
+      <c r="H12" s="18" t="n">
+        <f aca="false">IF(H11&lt;0,MIN(-H11,$M$12-H9),-MIN(H9,MAX(0,H11)))</f>
         <v>-0</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="K12" s="18" t="n">
+        <v>57</v>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="L12" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <f aca="false">IF(Cover!$C$11="Downside",L12,K12)</f>
         <v>40</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <f aca="false">C9+C12</f>
         <v>0.499999999999993</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <f aca="false">D9+D12</f>
         <v>0</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <f aca="false">E9+E12</f>
         <v>0</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="18" t="n">
         <f aca="false">F9+F12</f>
         <v>0</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="18" t="n">
         <f aca="false">G9+G12</f>
         <v>0</v>
       </c>
-      <c r="H13" s="17" t="n">
+      <c r="H13" s="18" t="n">
         <f aca="false">H9+H12</f>
         <v>0</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K13" s="16" t="n">
         <v>0.075</v>
       </c>
+      <c r="L13" s="16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M13" s="17" t="n">
+        <f aca="false">IF(Cover!$C$11="Downside",L13,K13)</f>
+        <v>0.075</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="C14" s="18" t="n">
         <f aca="false">MAX(0,MAX(0,C11)-C9)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <f aca="false">MAX(0,MAX(0,D11)-D9)</f>
         <v>3.42750000000001</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <f aca="false">MAX(0,MAX(0,E11)-E9)</f>
         <v>8.795090625</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="18" t="n">
         <f aca="false">MAX(0,MAX(0,F11)-F9)</f>
         <v>14.0967312929688</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="18" t="n">
         <f aca="false">MAX(0,MAX(0,G11)-G9)</f>
         <v>19.879299743501</v>
       </c>
-      <c r="H14" s="17" t="n">
+      <c r="H14" s="18" t="n">
         <f aca="false">MAX(0,MAX(0,H11)-H9)</f>
         <v>26.1795895739967</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="K14" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="M14" s="12" t="n">
         <f aca="false">'Sources &amp; Uses'!C6</f>
         <v>300</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J15" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="K15" s="13" t="n">
+        <v>62</v>
+      </c>
+      <c r="M15" s="12" t="n">
         <f aca="false">'Sources &amp; Uses'!C7</f>
         <v>200</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K16" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="M16" s="12" t="n">
         <f aca="false">'Sources &amp; Uses'!C5</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="17" t="n">
-        <f aca="false">$K$14</f>
+        <v>50</v>
+      </c>
+      <c r="C17" s="18" t="n">
+        <f aca="false">$M$14</f>
         <v>300</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <f aca="false">C20</f>
         <v>285</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="18" t="n">
         <f aca="false">D20</f>
         <v>267.429375</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="18" t="n">
         <f aca="false">E20</f>
         <v>245.83305703125</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="18" t="n">
         <f aca="false">F20</f>
         <v>220.260508561523</v>
       </c>
-      <c r="H17" s="17" t="n">
+      <c r="H17" s="18" t="n">
         <f aca="false">G20</f>
         <v>190.351033753898</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="17" t="n">
-        <f aca="false">MIN($K$14*$K$7,C17)</f>
+        <v>65</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <f aca="false">MIN($M$14*$M$7,C17)</f>
         <v>15</v>
       </c>
-      <c r="D18" s="17" t="n">
-        <f aca="false">MIN($K$14*$K$7,D17)</f>
+      <c r="D18" s="18" t="n">
+        <f aca="false">MIN($M$14*$M$7,D17)</f>
         <v>15</v>
       </c>
-      <c r="E18" s="17" t="n">
-        <f aca="false">MIN($K$14*$K$7,E17)</f>
+      <c r="E18" s="18" t="n">
+        <f aca="false">MIN($M$14*$M$7,E17)</f>
         <v>15</v>
       </c>
-      <c r="F18" s="17" t="n">
-        <f aca="false">MIN($K$14*$K$7,F17)</f>
+      <c r="F18" s="18" t="n">
+        <f aca="false">MIN($M$14*$M$7,F17)</f>
         <v>15</v>
       </c>
-      <c r="G18" s="17" t="n">
-        <f aca="false">MIN($K$14*$K$7,G17)</f>
+      <c r="G18" s="18" t="n">
+        <f aca="false">MIN($M$14*$M$7,G17)</f>
         <v>15</v>
       </c>
-      <c r="H18" s="17" t="n">
-        <f aca="false">MIN($K$14*$K$7,H17)</f>
+      <c r="H18" s="18" t="n">
+        <f aca="false">MIN($M$14*$M$7,H17)</f>
         <v>15</v>
       </c>
-      <c r="J18" s="19" t="s">
-        <v>62</v>
+      <c r="J18" s="20" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="17" t="n">
-        <f aca="false">MIN($K$11*C14,C17-C18)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="17" t="n">
-        <f aca="false">MIN($K$11*D14,D17-D18)</f>
+        <v>67</v>
+      </c>
+      <c r="C19" s="18" t="n">
+        <f aca="false">MIN($M$11*C14,C17-C18)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <f aca="false">MIN($M$11*D14,D17-D18)</f>
         <v>2.57062500000001</v>
       </c>
-      <c r="E19" s="17" t="n">
-        <f aca="false">MIN($K$11*E14,E17-E18)</f>
+      <c r="E19" s="18" t="n">
+        <f aca="false">MIN($M$11*E14,E17-E18)</f>
         <v>6.59631796875</v>
       </c>
-      <c r="F19" s="17" t="n">
-        <f aca="false">MIN($K$11*F14,F17-F18)</f>
+      <c r="F19" s="18" t="n">
+        <f aca="false">MIN($M$11*F14,F17-F18)</f>
         <v>10.5725484697266</v>
       </c>
-      <c r="G19" s="17" t="n">
-        <f aca="false">MIN($K$11*G14,G17-G18)</f>
+      <c r="G19" s="18" t="n">
+        <f aca="false">MIN($M$11*G14,G17-G18)</f>
         <v>14.9094748076257</v>
       </c>
-      <c r="H19" s="17" t="n">
-        <f aca="false">MIN($K$11*H14,H17-H18)</f>
+      <c r="H19" s="18" t="n">
+        <f aca="false">MIN($M$11*H14,H17-H18)</f>
         <v>19.6346921804975</v>
       </c>
-      <c r="J19" s="19" t="s">
-        <v>64</v>
+      <c r="J19" s="20" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="C20" s="18" t="n">
         <f aca="false">C17-C18-C19</f>
         <v>285</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="18" t="n">
         <f aca="false">D17-D18-D19</f>
         <v>267.429375</v>
       </c>
-      <c r="E20" s="17" t="n">
+      <c r="E20" s="18" t="n">
         <f aca="false">E17-E18-E19</f>
         <v>245.83305703125</v>
       </c>
-      <c r="F20" s="17" t="n">
+      <c r="F20" s="18" t="n">
         <f aca="false">F17-F18-F19</f>
         <v>220.260508561523</v>
       </c>
-      <c r="G20" s="17" t="n">
+      <c r="G20" s="18" t="n">
         <f aca="false">G17-G18-G19</f>
         <v>190.351033753898</v>
       </c>
-      <c r="H20" s="17" t="n">
+      <c r="H20" s="18" t="n">
         <f aca="false">H17-H18-H19</f>
         <v>155.7163415734</v>
       </c>
-      <c r="J20" s="19" t="s">
-        <v>65</v>
+      <c r="J20" s="20" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="17" t="n">
-        <f aca="false">C17*$K$8</f>
+        <v>52</v>
+      </c>
+      <c r="C21" s="18" t="n">
+        <f aca="false">C17*$M$8</f>
         <v>19.5</v>
       </c>
-      <c r="D21" s="17" t="n">
-        <f aca="false">D17*$K$8</f>
+      <c r="D21" s="18" t="n">
+        <f aca="false">D17*$M$8</f>
         <v>18.525</v>
       </c>
-      <c r="E21" s="17" t="n">
-        <f aca="false">E17*$K$8</f>
+      <c r="E21" s="18" t="n">
+        <f aca="false">E17*$M$8</f>
         <v>17.382909375</v>
       </c>
-      <c r="F21" s="17" t="n">
-        <f aca="false">F17*$K$8</f>
+      <c r="F21" s="18" t="n">
+        <f aca="false">F17*$M$8</f>
         <v>15.9791487070313</v>
       </c>
-      <c r="G21" s="17" t="n">
-        <f aca="false">G17*$K$8</f>
+      <c r="G21" s="18" t="n">
+        <f aca="false">G17*$M$8</f>
         <v>14.316933056499</v>
       </c>
-      <c r="H21" s="17" t="n">
-        <f aca="false">H17*$K$8</f>
+      <c r="H21" s="18" t="n">
+        <f aca="false">H17*$M$8</f>
         <v>12.3728171940034</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="17" t="n">
-        <f aca="false">$K$15</f>
+        <v>50</v>
+      </c>
+      <c r="C24" s="18" t="n">
+        <f aca="false">$M$15</f>
         <v>200</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="18" t="n">
         <f aca="false">C27</f>
         <v>198</v>
       </c>
-      <c r="E24" s="17" t="n">
+      <c r="E24" s="18" t="n">
         <f aca="false">D27</f>
         <v>196</v>
       </c>
-      <c r="F24" s="17" t="n">
+      <c r="F24" s="18" t="n">
         <f aca="false">E27</f>
         <v>194</v>
       </c>
-      <c r="G24" s="17" t="n">
+      <c r="G24" s="18" t="n">
         <f aca="false">F27</f>
         <v>192</v>
       </c>
-      <c r="H24" s="17" t="n">
+      <c r="H24" s="18" t="n">
         <f aca="false">G27</f>
         <v>190</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="17" t="n">
-        <f aca="false">MIN($K$15*$K$9,C24)</f>
+        <v>65</v>
+      </c>
+      <c r="C25" s="18" t="n">
+        <f aca="false">MIN($M$15*$M$9,C24)</f>
         <v>2</v>
       </c>
-      <c r="D25" s="17" t="n">
-        <f aca="false">MIN($K$15*$K$9,D24)</f>
+      <c r="D25" s="18" t="n">
+        <f aca="false">MIN($M$15*$M$9,D24)</f>
         <v>2</v>
       </c>
-      <c r="E25" s="17" t="n">
-        <f aca="false">MIN($K$15*$K$9,E24)</f>
+      <c r="E25" s="18" t="n">
+        <f aca="false">MIN($M$15*$M$9,E24)</f>
         <v>2</v>
       </c>
-      <c r="F25" s="17" t="n">
-        <f aca="false">MIN($K$15*$K$9,F24)</f>
+      <c r="F25" s="18" t="n">
+        <f aca="false">MIN($M$15*$M$9,F24)</f>
         <v>2</v>
       </c>
-      <c r="G25" s="17" t="n">
-        <f aca="false">MIN($K$15*$K$9,G24)</f>
+      <c r="G25" s="18" t="n">
+        <f aca="false">MIN($M$15*$M$9,G24)</f>
         <v>2</v>
       </c>
-      <c r="H25" s="17" t="n">
-        <f aca="false">MIN($K$15*$K$9,H24)</f>
+      <c r="H25" s="18" t="n">
+        <f aca="false">MIN($M$15*$M$9,H24)</f>
         <v>2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="17" t="n">
-        <f aca="false">MIN($K$11*C14-C19,C24-C25)</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="17" t="n">
-        <f aca="false">MIN($K$11*D14-D19,D24-D25)</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="17" t="n">
-        <f aca="false">MIN($K$11*E14-E19,E24-E25)</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="17" t="n">
-        <f aca="false">MIN($K$11*F14-F19,F24-F25)</f>
-        <v>0</v>
-      </c>
-      <c r="G26" s="17" t="n">
-        <f aca="false">MIN($K$11*G14-G19,G24-G25)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="17" t="n">
-        <f aca="false">MIN($K$11*H14-H19,H24-H25)</f>
+        <v>72</v>
+      </c>
+      <c r="C26" s="18" t="n">
+        <f aca="false">MIN($M$11*C14-C19,C24-C25)</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <f aca="false">MIN($M$11*D14-D19,D24-D25)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <f aca="false">MIN($M$11*E14-E19,E24-E25)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <f aca="false">MIN($M$11*F14-F19,F24-F25)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="18" t="n">
+        <f aca="false">MIN($M$11*G14-G19,G24-G25)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="18" t="n">
+        <f aca="false">MIN($M$11*H14-H19,H24-H25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="C27" s="18" t="n">
         <f aca="false">C24-C25-C26</f>
         <v>198</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="18" t="n">
         <f aca="false">D24-D25-D26</f>
         <v>196</v>
       </c>
-      <c r="E27" s="17" t="n">
+      <c r="E27" s="18" t="n">
         <f aca="false">E24-E25-E26</f>
         <v>194</v>
       </c>
-      <c r="F27" s="17" t="n">
+      <c r="F27" s="18" t="n">
         <f aca="false">F24-F25-F26</f>
         <v>192</v>
       </c>
-      <c r="G27" s="17" t="n">
+      <c r="G27" s="18" t="n">
         <f aca="false">G24-G25-G26</f>
         <v>190</v>
       </c>
-      <c r="H27" s="17" t="n">
+      <c r="H27" s="18" t="n">
         <f aca="false">H24-H25-H26</f>
         <v>188</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" s="17" t="n">
-        <f aca="false">C24*$K$10</f>
+        <v>52</v>
+      </c>
+      <c r="C28" s="18" t="n">
+        <f aca="false">C24*$M$10</f>
         <v>19</v>
       </c>
-      <c r="D28" s="17" t="n">
-        <f aca="false">D24*$K$10</f>
+      <c r="D28" s="18" t="n">
+        <f aca="false">D24*$M$10</f>
         <v>18.81</v>
       </c>
-      <c r="E28" s="17" t="n">
-        <f aca="false">E24*$K$10</f>
+      <c r="E28" s="18" t="n">
+        <f aca="false">E24*$M$10</f>
         <v>18.62</v>
       </c>
-      <c r="F28" s="17" t="n">
-        <f aca="false">F24*$K$10</f>
+      <c r="F28" s="18" t="n">
+        <f aca="false">F24*$M$10</f>
         <v>18.43</v>
       </c>
-      <c r="G28" s="17" t="n">
-        <f aca="false">G24*$K$10</f>
+      <c r="G28" s="18" t="n">
+        <f aca="false">G24*$M$10</f>
         <v>18.24</v>
       </c>
-      <c r="H28" s="17" t="n">
-        <f aca="false">H24*$K$10</f>
+      <c r="H28" s="18" t="n">
+        <f aca="false">H24*$M$10</f>
         <v>18.05</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C30" s="9" t="n">
         <f aca="false">C13+C20+C27</f>
@@ -1853,7 +1955,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C31" s="9" t="n">
         <f aca="false">C10+C21+C28</f>
@@ -1882,29 +1984,29 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" s="20" t="n">
+        <v>75</v>
+      </c>
+      <c r="C32" s="21" t="n">
         <f aca="false">IFERROR(C30/C5,"-")</f>
         <v>4.835</v>
       </c>
-      <c r="D32" s="20" t="n">
+      <c r="D32" s="21" t="n">
         <f aca="false">IFERROR(D30/D5,"-")</f>
         <v>4.37197523584906</v>
       </c>
-      <c r="E32" s="20" t="n">
+      <c r="E32" s="21" t="n">
         <f aca="false">IFERROR(E30/E5,"-")</f>
         <v>3.91449854958393</v>
       </c>
-      <c r="F32" s="20" t="n">
+      <c r="F32" s="21" t="n">
         <f aca="false">IFERROR(F30/F5,"-")</f>
         <v>3.46141872620958</v>
       </c>
-      <c r="G32" s="20" t="n">
+      <c r="G32" s="21" t="n">
         <f aca="false">IFERROR(G30/G5,"-")</f>
         <v>3.01273643642493</v>
       </c>
-      <c r="H32" s="20" t="n">
+      <c r="H32" s="21" t="n">
         <f aca="false">IFERROR(H30/H5,"-")</f>
         <v>2.56844845388345</v>
       </c>
@@ -1925,7 +2027,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:D33"/>
+  <dimension ref="B2:E33"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
@@ -1935,33 +2037,33 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="5" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="21" t="n">
+        <v>78</v>
+      </c>
+      <c r="C5" s="22" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="22" t="n">
+        <v>79</v>
+      </c>
+      <c r="C6" s="23" t="n">
         <v>7.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C7" s="9" t="n">
         <f aca="false">C5*C6</f>
@@ -1970,38 +2072,51 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="23" t="n">
+        <v>81</v>
+      </c>
+      <c r="C8" s="24" t="n">
         <f aca="false">'Sources &amp; Uses'!C9</f>
         <v>200</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="23" t="n">
+        <v>83</v>
+      </c>
+      <c r="C11" s="24" t="n">
         <f aca="false">'Debt Schedule'!H5</f>
         <v>133.82255776</v>
       </c>
+      <c r="D11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="22" t="n">
+        <v>84</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <f aca="false">IFERROR(IF(Cover!$C$11="Downside",E12,D12),"-")</f>
         <v>8</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C13" s="9" t="n">
         <f aca="false">C11*C12</f>
@@ -2010,16 +2125,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="23" t="n">
+        <v>86</v>
+      </c>
+      <c r="C14" s="24" t="n">
         <f aca="false">'Debt Schedule'!H30</f>
         <v>343.7163415734</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C15" s="8" t="n">
         <f aca="false">C13-C14</f>
@@ -2028,142 +2143,142 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="24" t="n">
+        <v>89</v>
+      </c>
+      <c r="C18" s="26" t="n">
         <f aca="false">IFERROR(C15/(C8+'Sources &amp; Uses'!C10),"-")</f>
         <v>2.9074564820264</v>
       </c>
-      <c r="D18" s="19" t="s">
-        <v>85</v>
+      <c r="D18" s="20" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="C19" s="11" t="n">
         <f aca="false">Cover!C9</f>
         <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" s="25" t="n">
+        <v>92</v>
+      </c>
+      <c r="C20" s="27" t="n">
         <f aca="false">IFERROR(C18^(1/C19)-1,"-")</f>
         <v>0.237948690048196</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" s="13" t="n">
+        <v>94</v>
+      </c>
+      <c r="C23" s="12" t="n">
         <f aca="false">'Sources &amp; Uses'!C9+'Sources &amp; Uses'!C10</f>
         <v>250</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" s="26" t="n">
+        <v>95</v>
+      </c>
+      <c r="C24" s="15" t="n">
         <f aca="false">IFERROR('Sources &amp; Uses'!C10/C23,"-")</f>
         <v>0.2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" s="15" t="n">
+        <v>96</v>
+      </c>
+      <c r="C25" s="14" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="15" t="n">
+        <v>97</v>
+      </c>
+      <c r="C26" s="14" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="14" t="n">
+        <v>98</v>
+      </c>
+      <c r="C27" s="13" t="n">
         <f aca="false">IFERROR(C23*(1+C25)^C19,"-")</f>
         <v>622.08</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="C28" s="13" t="n">
         <f aca="false">MAX(0,C15-C27)</f>
         <v>104.7841205066</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C29" s="27" t="n">
+        <v>100</v>
+      </c>
+      <c r="C29" s="28" t="n">
         <f aca="false">C28*C26</f>
         <v>20.95682410132</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C30" s="27" t="n">
+        <v>101</v>
+      </c>
+      <c r="C30" s="28" t="n">
         <f aca="false">IFERROR(C24*C15+C29,"-")</f>
         <v>166.32964820264</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C31" s="27" t="n">
+        <v>102</v>
+      </c>
+      <c r="C31" s="28" t="n">
         <f aca="false">IFERROR(C15-C30,"-")</f>
         <v>560.53447230396</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C32" s="28" t="n">
+        <v>103</v>
+      </c>
+      <c r="C32" s="29" t="n">
         <f aca="false">IFERROR(C31/'Sources &amp; Uses'!C9,"-")</f>
         <v>2.8026723615198</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" s="29" t="n">
+        <v>104</v>
+      </c>
+      <c r="C33" s="30" t="n">
         <f aca="false">IFERROR(C32^(1/C19)-1,"-")</f>
         <v>0.228894119802123</v>
       </c>
-      <c r="D33" s="19" t="s">
-        <v>100</v>
+      <c r="D33" s="20" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2192,127 +2307,127 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" s="30" t="n">
+        <v>107</v>
+      </c>
+      <c r="C4" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="D4" s="30" t="n">
+      <c r="D4" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="30" t="n">
+      <c r="E4" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="F4" s="30" t="n">
+      <c r="F4" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="30" t="n">
+      <c r="G4" s="31" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="30" t="n">
+      <c r="B5" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>103</v>
+      <c r="C5" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30" t="n">
+      <c r="B6" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>103</v>
+      <c r="C6" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="30" t="n">
+      <c r="B7" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>103</v>
+      <c r="C7" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30" t="n">
+      <c r="B8" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="C8" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>103</v>
+      <c r="C8" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="30" t="n">
+      <c r="B9" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="C9" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>103</v>
+      <c r="C9" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2343,24 +2458,24 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="10" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2368,30 +2483,30 @@
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>6</v>
@@ -2402,13 +2517,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>8</v>

--- a/03_Private_Equity/deals/PROJECT_ATLAS.xlsx
+++ b/03_Private_Equity/deals/PROJECT_ATLAS.xlsx
@@ -571,127 +571,127 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
